--- a/relationship_surveys/001_youth_climate_policy_understanding_survey--relationship_surveys.xlsx
+++ b/relationship_surveys/001_youth_climate_policy_understanding_survey--relationship_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -798,12 +798,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'0'}</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': '0'}</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -815,12 +815,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'1'}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': '1'}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -832,12 +832,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'2'}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': '2'}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -849,12 +849,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'3'}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': '3'}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -866,12 +866,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'4'}</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': '4'}</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -883,12 +883,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'5'}</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': '5'}</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -900,12 +900,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'male'}</t>
+          <t>male</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'Male'}</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -917,12 +917,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'female'}</t>
+          <t>female</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Female'}</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -934,12 +934,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -951,12 +951,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_4,_'label':_'non-binary'}</t>
+          <t>non-binary</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 4, 'label': 'Non-binary'}</t>
+          <t>Non-binary</t>
         </is>
       </c>
     </row>
@@ -968,12 +968,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'climate_change_and_global_warming'}</t>
+          <t>climate_change_and_global_warming</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'Climate change and global warming'}</t>
+          <t>Climate change and global warming</t>
         </is>
       </c>
     </row>
@@ -985,12 +985,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'economic_inequality_and_poverty'}</t>
+          <t>economic_inequality_and_poverty</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Economic inequality and poverty'}</t>
+          <t>Economic inequality and poverty</t>
         </is>
       </c>
     </row>
@@ -1002,12 +1002,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'racial_and_social_injustice'}</t>
+          <t>racial_and_social_injustice</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Racial and social injustice'}</t>
+          <t>Racial and social injustice</t>
         </is>
       </c>
     </row>
@@ -1019,12 +1019,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_4,_'label':_'war_and_conflict'}</t>
+          <t>war_and_conflict</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 4, 'label': 'War and conflict'}</t>
+          <t>War and conflict</t>
         </is>
       </c>
     </row>
@@ -1036,12 +1036,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_5,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 5, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1053,12 +1053,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'reducing_greenhouse_gas_emissions'}</t>
+          <t>reducing_greenhouse_gas_emissions</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'Reducing greenhouse gas emissions'}</t>
+          <t>Reducing greenhouse gas emissions</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'creating_more_jobs_and_opportunities_for_young_people'}</t>
+          <t>creating_more_jobs_and_opportunities_for_young_people</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Creating more jobs and opportunities for young people'}</t>
+          <t>Creating more jobs and opportunities for young people</t>
         </is>
       </c>
     </row>
@@ -1087,12 +1087,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'improving_public_transportation_and_urban_planning'}</t>
+          <t>improving_public_transportation_and_urban_planning</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Improving public transportation and urban planning'}</t>
+          <t>Improving public transportation and urban planning</t>
         </is>
       </c>
     </row>
@@ -1104,12 +1104,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_4,_'label':_'protecting_and_conserving_natural_spaces'}</t>
+          <t>protecting_and_conserving_natural_spaces</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 4, 'label': 'Protecting and conserving natural spaces'}</t>
+          <t>Protecting and conserving natural spaces</t>
         </is>
       </c>
     </row>
@@ -1121,12 +1121,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_5,_'label':_'increasing_public_awareness'}</t>
+          <t>increasing_public_awareness</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 5, 'label': 'Increasing public awareness'}</t>
+          <t>Increasing public awareness</t>
         </is>
       </c>
     </row>
@@ -1138,12 +1138,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'reduce_greenhouse_gas_emissions'}</t>
+          <t>reduce_greenhouse_gas_emissions</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'Reduce greenhouse gas emissions'}</t>
+          <t>Reduce greenhouse gas emissions</t>
         </is>
       </c>
     </row>
@@ -1155,12 +1155,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'create_more_jobs_and_opportunities'}</t>
+          <t>create_more_jobs_and_opportunities</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Create more jobs and opportunities'}</t>
+          <t>Create more jobs and opportunities</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1172,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'improve_public_transportation_and_urban_planning'}</t>
+          <t>improve_public_transportation_and_urban_planning</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Improve public transportation and urban planning'}</t>
+          <t>Improve public transportation and urban planning</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'value':_4,_'label':_'protect_natural_spaces'}</t>
+          <t>protect_natural_spaces</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'value': 4, 'label': 'Protect natural spaces'}</t>
+          <t>Protect natural spaces</t>
         </is>
       </c>
     </row>
@@ -1206,12 +1206,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'value':_5,_'label':_'increase_public_awareness_and_education'}</t>
+          <t>increase_public_awareness_and_education</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'value': 5, 'label': 'Increase public awareness and education'}</t>
+          <t>Increase public awareness and education</t>
         </is>
       </c>
     </row>
@@ -1223,12 +1223,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'value':_6,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'value': 6, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
